--- a/data/past_lives.xlsx
+++ b/data/past_lives.xlsx
@@ -428,15 +428,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,25 +448,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>분류</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>전생의 직업 또는 존재</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>시대</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>사인(죽은 이유)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>전생의 업적</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>사람들의 기억</t>
         </is>
@@ -477,25 +483,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>사람</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>호모 에렉투스 사냥꾼</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>기원전 약 140만 년</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>검치호랑이의 습격을 받아 사망</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>무리 최초로 돌창 끝을 뾰족하게 다듬어 큰 사냥을 성공시킴</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>'두려움을 모르는 손'으로 동굴 벽 손자국에 남음</t>
         </is>
@@ -507,27 +518,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>불씨를 지키는 사람</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>기원전 약 90만 년</t>
+          <t>검치호랑이(스밀로돈)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>혹독한 겨울 추위로 얼어 죽음</t>
+          <t>기원전 약 100만 년</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>꺼지지 않는 불씨를 여러 세대에 걸쳐 지켜냄</t>
+          <t>늙어 사냥에 실패하고 굶주려 죽음</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>무리의 '불의 어머니'로 이야기됨</t>
+          <t>초원 최강의 포식자로 오래 군림</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>긴 송곳니의 전설로 후대에 회자됨</t>
         </is>
       </c>
     </row>
@@ -537,27 +553,32 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>털매머드</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>기원전 약 50만 년</t>
+          <t>최초의 손도끼 장인</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>빙하기 말 먹이 부족으로 쇠약해져 죽음</t>
+          <t>기원전 약 80만 년</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>거대한 상아로 무리를 이끌며 초원을 지배</t>
+          <t>노환으로 평온히 눈을 감음</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>초원의 왕으로 사냥꾼들의 벽화에 새겨짐</t>
+          <t>더 날카롭고 균형 잡힌 손도끼를 고안</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>'돌을 길들인 손'으로 존경받음</t>
         </is>
       </c>
     </row>
@@ -567,27 +588,32 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>검치호랑이(스밀로돈)</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>기원전 약 100만 년</t>
+          <t>털매머드</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>늙어 사냥에 실패하고 굶주려 죽음</t>
+          <t>기원전 약 50만 년</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>초원 최강의 포식자로 오래 군림</t>
+          <t>빙하기 말 먹이 부족으로 쇠약해져 죽음</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>긴 송곳니의 전설로 후대에 회자됨</t>
+          <t>거대한 상아로 무리를 이끌며 초원을 지배</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>초원의 왕으로 사냥꾼들의 벽화에 새겨짐</t>
         </is>
       </c>
     </row>
@@ -597,27 +623,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>동굴곰</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>기원전 약 30만 년</t>
+          <t>거대사슴 메갈로케로스</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>겨울잠 중 동굴이 무너져 사망</t>
+          <t>기원전 약 40만 년</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>가장 깊고 따뜻한 동굴을 차지한 우두머리</t>
+          <t>늪에 거대한 뿔이 걸려 익사</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>동굴 벽의 긁힌 발톱 자국으로 흔적을 남김</t>
+          <t>3미터가 넘는 뿔로 숲을 호령</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>가장 웅장한 뿔의 주인으로 남음</t>
         </is>
       </c>
     </row>
@@ -627,27 +658,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>라스코의 동굴 화가</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>기원전 약 17000년</t>
+          <t>동굴곰</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>사냥 중 절벽에서 추락</t>
+          <t>기원전 약 30만 년</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>동굴 깊은 곳에 들소 떼를 생생히 그림</t>
+          <t>겨울잠 중 동굴이 무너져 사망</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>'벽에 생명을 불어넣은 손'으로 전해짐</t>
+          <t>가장 깊고 따뜻한 동굴을 차지한 우두머리</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>동굴 벽의 긁힌 발톱 자국으로 흔적을 남김</t>
         </is>
       </c>
     </row>
@@ -657,27 +693,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>별을 읽는 주술사</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>기원전 약 20000년</t>
+          <t>빙하기의 동굴 사자</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>오랜 병을 앓다 사망</t>
+          <t>기원전 약 30만 년</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>별의 움직임으로 계절과 사냥철을 예언</t>
+          <t>먹이를 두고 무리와 다투다 부상으로 죽음</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>무리의 '하늘을 읽는 자'로 기억됨</t>
+          <t>얼어붙은 초원의 최상위 포식자로 군림</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>동굴 벽에 붉은 갈기로 그려져 남음</t>
         </is>
       </c>
     </row>
@@ -687,27 +728,32 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>거대사슴 메갈로케로스</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>기원전 약 40만 년</t>
+          <t>털코뿔소</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>늪에 거대한 뿔이 걸려 익사</t>
+          <t>기원전 약 25만 년</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3미터가 넘는 뿔로 숲을 호령</t>
+          <t>빙하기 혹한을 견디지 못하고 죽음</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>가장 웅장한 뿔의 주인으로 남음</t>
+          <t>두꺼운 털가죽으로 툰드라를 홀로 누빔</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>얼음 벌판의 외로운 전사로 전해짐</t>
         </is>
       </c>
     </row>
@@ -717,27 +763,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>털코뿔소</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>기원전 약 25만 년</t>
+          <t>빙하기의 잿빛 늑대 우두머리</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>빙하기 혹한을 견디지 못하고 죽음</t>
+          <t>기원전 약 2만 년</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>두꺼운 털가죽으로 툰드라를 홀로 누빔</t>
+          <t>혹한의 사냥철 굶주림 속에 무리를 지키다 죽음</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>얼음 벌판의 외로운 전사로 전해짐</t>
+          <t>거대한 무리를 이끌어 순록 떼를 사냥</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>'달을 향해 우는 우두머리'로 사냥꾼의 그림에 남음</t>
         </is>
       </c>
     </row>
@@ -747,27 +798,32 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>최초의 손도끼 장인</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>기원전 약 80만 년</t>
+          <t>라스코의 동굴 화가</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>노환으로 평온히 눈을 감음</t>
+          <t>기원전 약 17000년</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>더 날카롭고 균형 잡힌 손도끼를 고안</t>
+          <t>사냥 중 절벽에서 추락</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>'돌을 길들인 손'으로 존경받음</t>
+          <t>동굴 깊은 곳에 들소 떼를 생생히 그림</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>'벽에 생명을 불어넣은 손'으로 전해짐</t>
         </is>
       </c>
     </row>
@@ -777,25 +833,30 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>사람</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>동굴 무리의 치료사</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>기원전 약 15000년</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>역병을 돌보다 감염되어 사망</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>약초로 상처와 열병을 다스림</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>'낫게 하는 손'으로 무리의 사랑을 받음</t>
         </is>
@@ -807,25 +868,30 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>생물</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>들소 무리의 우두머리</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>기원전 약 12000년</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>늑대 무리에 맞서다 부상으로 죽음</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>거대한 들소 떼를 안전한 초지로 이끎</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>초원을 뒤흔든 발굽 소리로 기억됨</t>
         </is>
@@ -837,27 +903,32 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>최초의 밀 농부</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>기원전 9000년경</t>
+          <t>초원을 달린 야생마 타르판</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>홍수에 밭과 함께 휩쓸려 사망</t>
+          <t>기원전 약 8000년</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>야생 밀을 길들여 마을에 정착 농경을 시작</t>
+          <t>사냥꾼의 몰이에 절벽으로 내몰려 떨어짐</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>'땅을 먹인 사람'으로 마을 전설에 남음</t>
+          <t>길들여지지 않은 자유로운 무리로 초원을 누빔</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>'바람의 갈기'로 동굴 벽화에 남음</t>
         </is>
       </c>
     </row>
@@ -867,25 +938,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>사람</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>메소포타미아 점토판 서기</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>기원전 3200년경</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>열병으로 젊은 나이에 사망</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>쐐기문자로 최초의 곡물 장부를 기록</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>'글자를 새긴 자'로 신전 기록에 이름을 남김</t>
         </is>
@@ -897,27 +973,32 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>수메르 맥주 양조사</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>기원전 3000년경</t>
+          <t>신단수라 불린 신령한 나무</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>기원전 2333년경</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>보리로 최초의 맥주 제조법을 완성</t>
+          <t>번개를 맞고도 오래 버티다 끝내 삭아 쓰러짐</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>여신 닌카시의 사랑을 받은 양조사로 노래됨</t>
+          <t>하늘과 땅을 잇는 신단수로 사람들의 기도를 받음</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>'하늘로 통하는 나무'로 건국 신화에 남음</t>
         </is>
       </c>
     </row>
@@ -927,27 +1008,32 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>이집트 왕실 서기관</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>기원전 1350년경</t>
+          <t>고대 동방의 용(龍)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>나일강 범람기 열병으로 사망</t>
+          <t>기원전 2000년경</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>파라오의 곡물 창고 장부를 20년간 관리해 기근을 막음</t>
+          <t>하늘로 승천하다 벼락과 부딪혀 사라짐</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>'글자를 아는 현명한 손'으로 벽화에 새겨짐</t>
+          <t>구름과 비를 부려 가뭄 든 땅에 단비를 내림</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>'비를 부르는 신수'로 사당의 벽화에 새겨짐</t>
         </is>
       </c>
     </row>
@@ -957,27 +1043,32 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>이집트 신전의 고양이</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>기원전 1300년경</t>
+          <t>불사조 봉황(鳳凰)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>노환으로 신전에서 잠들 듯 죽음</t>
+          <t>기원전 1500년경</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>곡물 창고의 쥐를 지켜 신관들의 사랑을 받음</t>
+          <t>스스로 불길에 몸을 던져 재가 되었다 다시 태어남</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>여신 바스테트의 화신으로 미라가 되어 모셔짐</t>
+          <t>태평성대에만 나타나 상서로움을 알림</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>'다시 태어나는 새'로 궁궐 지붕을 지키는 상징이 됨</t>
         </is>
       </c>
     </row>
@@ -987,27 +1078,32 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>피라미드 석공</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>기원전 2560년경</t>
+          <t>이집트 파라오의 사냥개</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>돌을 나르다 사고로 사망</t>
+          <t>기원전 1400년경</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>쿠푸 대피라미드의 외장석을 다듬음</t>
+          <t>노환으로 죽어 주인 곁에 묻힘</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>'돌을 노래하게 한 손'으로 동료들 사이에 전해짐</t>
+          <t>사냥터에서 파라오를 도와 짐승을 몰았음</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>'왕의 발치를 지킨 개'로 무덤 벽화에 남음</t>
         </is>
       </c>
     </row>
@@ -1017,27 +1113,32 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>바빌론 점성술사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>기원전 600년경</t>
+          <t>이집트 왕실 서기관</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>왕의 노여움을 사 독살됨</t>
+          <t>기원전 1350년경</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>행성의 운행을 기록해 달력을 정교하게 다듬음</t>
+          <t>나일강 범람기 열병으로 사망</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>'밤하늘의 예언자'로 궁정 기록에 남음</t>
+          <t>파라오의 곡물 창고 장부를 20년간 관리해 기근을 막음</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>'글자를 아는 현명한 손'으로 벽화에 새겨짐</t>
         </is>
       </c>
     </row>
@@ -1047,27 +1148,32 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>페니키아 항해사</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>기원전 500년경</t>
+          <t>이집트 신전의 고양이</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>지중해 폭풍에 배가 침몰해 익사</t>
+          <t>기원전 1300년경</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>별을 보고 아프리카 해안을 일주함</t>
+          <t>노환으로 신전에서 잠들 듯 죽음</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>'바다에 길을 낸 자'로 항구마다 이야기됨</t>
+          <t>곡물 창고의 쥐를 지켜 신관들의 사랑을 받음</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>여신 바스테트의 화신으로 미라가 되어 모셔짐</t>
         </is>
       </c>
     </row>
@@ -1077,27 +1183,32 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>고대 그리스 철학자</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>기원전 400년경</t>
+          <t>나일강의 신성한 따오기</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>노환으로 제자들에 둘러싸여 사망</t>
+          <t>기원전 1100년경</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>만물의 근원을 논하며 학당을 세움</t>
+          <t>노환으로 신전 정원에서 죽어 미라가 됨</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>'질문하는 자'로 후대 철학자들이 인용함</t>
+          <t>지혜의 신 토트의 화신으로 여겨져 숭배받음</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>'달의 새'로 파피루스와 벽화에 그려짐</t>
         </is>
       </c>
     </row>
@@ -1107,27 +1218,32 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>올림피아의 달리기 선수</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>기원전 480년경</t>
+          <t>고대 이집트의 미라 제작 사제</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>훈련 중 심장이 멎어 사망</t>
+          <t>기원전 1000년경</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>고대 올림픽 단거리에서 세 번 우승</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>월계관을 쓴 '바람의 다리'로 조각에 남음</t>
+          <t>영혼의 여행을 위해 정성껏 미라를 만듦</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>'죽음을 지킨 손'으로 신전 기록에 남음</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1253,32 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>스파르타 전사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>기원전 480년경</t>
+          <t>바빌론 점성술사</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>테르모필라이 협곡 전투에서 전사</t>
+          <t>기원전 600년경</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>소수로 대군을 막아 시간을 벌어줌</t>
+          <t>왕의 노여움을 사 독살됨</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>'물러서지 않은 방패'로 비석에 새겨짐</t>
+          <t>행성의 운행을 기록해 달력을 정교하게 다듬음</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>'밤하늘의 예언자'로 궁정 기록에 남음</t>
         </is>
       </c>
     </row>
@@ -1167,27 +1288,32 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>한니발의 전투 코끼리</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>기원전 218년경</t>
+          <t>델포이의 신성한 비둘기</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>알프스를 넘다 추위와 굶주림으로 죽음</t>
+          <t>기원전 500년경</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>험준한 산맥을 넘어 로마군을 놀라게 함</t>
+          <t>신탁을 전하러 날다 매에게 잡혀 죽음</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>'산을 넘은 거인'으로 전쟁 기록에 남음</t>
+          <t>신전의 예언을 사람들에게 물어 날랐다고 전해짐</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>'신의 전령'으로 순례자들이 기림</t>
         </is>
       </c>
     </row>
@@ -1197,27 +1323,32 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>로마 검투사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>서기 80년경</t>
+          <t>고대 페르시아의 파발 전령</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>콜로세움 결투에서 부상으로 사망</t>
+          <t>기원전 500년경</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50번의 결투에서 살아남아 목검(자유)을 받음</t>
+          <t>먼 길을 달리다 탈진으로 사망</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>관중이 이름을 연호한 '모래판의 사자'로 기억됨</t>
+          <t>'왕의 길'을 릴레이로 달려 칙령을 전함</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>'비도 눈도 막지 못한 전령'으로 칭송됨</t>
         </is>
       </c>
     </row>
@@ -1227,27 +1358,32 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>로마 군단의 군마</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>서기 100년경</t>
+          <t>스파르타 전사</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>원정 행군 중 늙어 쓰러짐</t>
+          <t>기원전 480년경</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>장군을 태우고 갈리아 전역을 누빔</t>
+          <t>테르모필라이 협곡 전투에서 전사</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>'멈추지 않는 발굽'으로 병사들에게 사랑받음</t>
+          <t>소수로 대군을 막아 시간을 벌어줌</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>'물러서지 않은 방패'로 비석에 새겨짐</t>
         </is>
       </c>
     </row>
@@ -1257,27 +1393,32 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>로마 수도교 기술자</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>서기 120년경</t>
+          <t>아테나 신전의 올빼미</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>공사 중 비계가 무너져 사망</t>
+          <t>기원전 450년경</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>도시에 맑은 물을 나르는 수도교를 설계</t>
+          <t>신전이 불타던 밤 연기에 스러짐</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>'물길을 놓은 사람'으로 도시가 기억함</t>
+          <t>밤마다 지혜의 여신 곁을 지킴</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>'지혜의 눈'으로 은화에 새겨져 오래 남음</t>
         </is>
       </c>
     </row>
@@ -1287,27 +1428,32 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>진나라 만리장성 축조공</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>기원전 214년경</t>
+          <t>고대 그리스 철학자</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>혹독한 노역 끝에 병으로 사망</t>
+          <t>기원전 400년경</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>북방 성벽의 한 구간을 쌓아 올림</t>
+          <t>노환으로 제자들에 둘러싸여 사망</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>이름 없는 '벽을 세운 손' 중 하나로 남음</t>
+          <t>만물의 근원을 논하며 학당을 세움</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>'질문하는 자'로 후대 철학자들이 인용함</t>
         </is>
       </c>
     </row>
@@ -1317,27 +1463,32 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>한나라 비단길 대상</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>기원전 100년경</t>
+          <t>고조선 청동검 장인</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>사막에서 모래폭풍을 만나 실종</t>
+          <t>기원전 400년경</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>장안에서 서역까지 비단을 실어 나름</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>'사막에 길을 튼 상인'으로 객잔마다 이야기됨</t>
+          <t>비파형 동검을 정교하게 주조</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>'청동에 혼을 담은 손'으로 부족이 기림</t>
         </is>
       </c>
     </row>
@@ -1347,27 +1498,32 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>마야 천문 사제</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>서기 300년경</t>
+          <t>한니발의 전투 코끼리</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>제례 중 지진으로 신전과 함께 매몰</t>
+          <t>기원전 218년경</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>금성의 주기를 계산해 정교한 달력을 만듦</t>
+          <t>알프스를 넘다 추위와 굶주림으로 죽음</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>'하늘의 시간을 읽은 자'로 석비에 새겨짐</t>
+          <t>험준한 산맥을 넘어 로마군을 놀라게 함</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>'산을 넘은 거인'으로 전쟁 기록에 남음</t>
         </is>
       </c>
     </row>
@@ -1377,27 +1533,32 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>나스카 지상화 장인</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>서기 400년경</t>
+          <t>진나라 만리장성 축조공</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>사막의 열사병으로 사망</t>
+          <t>기원전 214년경</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>거대한 벌새 그림을 대지에 새김</t>
+          <t>혹독한 노역 끝에 병으로 사망</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>'하늘만이 볼 수 있는 그림'을 남긴 자로 전해짐</t>
+          <t>북방 성벽의 한 구간을 쌓아 올림</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>이름 없는 '벽을 세운 손' 중 하나로 남음</t>
         </is>
       </c>
     </row>
@@ -1407,27 +1568,32 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>고조선 청동검 장인</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>기원전 400년경</t>
+          <t>고대 인도 아유르베다 의사</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>기원전 200년경</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>노환으로 사망</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>비파형 동검을 정교하게 주조</t>
-        </is>
-      </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>'청동에 혼을 담은 손'으로 부족이 기림</t>
+          <t>약초와 명상으로 몸과 마음을 함께 치료</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>'생명의 지혜를 전한 자'로 경전에 남음</t>
         </is>
       </c>
     </row>
@@ -1437,27 +1603,32 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>페르시아 양탄자 직조공</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>서기 450년경</t>
+          <t>고대 로마의 포도밭 농부</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>시력을 잃고 노년에 사망</t>
+          <t>서기 50년경</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>천 개의 매듭으로 정원을 담은 양탄자를 짬</t>
+          <t>포도 수확 중 사고로 사망</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>'실로 낙원을 그린 손'으로 왕실이 아낌</t>
+          <t>언덕에 포도를 길러 향기로운 포도주를 빚음</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>'햇빛을 술로 바꾼 손'으로 마을이 기림</t>
         </is>
       </c>
     </row>
@@ -1467,25 +1638,30 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
+          <t>사람</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
           <t>켈트족 드루이드</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>서기 60년경</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>성림(聖林)을 지키다 로마군에 사망</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>떡갈나무 숲에서 별과 계절의 지혜를 전함</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>'숲의 목소리'로 노래와 전설에 남음</t>
         </is>
@@ -1497,27 +1673,32 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>수도원의 필사 수도사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>800년경</t>
+          <t>폼페이의 빵집 주인</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>노환으로 수도원에서 사망</t>
+          <t>서기 79년</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>성서를 금박 삽화와 함께 필사해 남김</t>
+          <t>베수비오 화산 폭발로 화산재에 묻힘</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>'빛을 그린 손'으로 필사본에 이름이 전함</t>
+          <t>매일 아침 도시에 갓 구운 빵을 냄</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>화산재 속 화덕과 함께 '멈춘 아침'으로 발굴됨</t>
         </is>
       </c>
     </row>
@@ -1527,27 +1708,32 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>수도원의 고양이 판구르 반</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>850년경</t>
+          <t>로마 검투사</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>난롯가에서 노환으로 잠들 듯 죽음</t>
+          <t>서기 80년경</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>필사실의 쥐를 지켜 수도사의 벗이 됨</t>
+          <t>콜로세움 결투에서 부상으로 사망</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>한 수도사의 시(詩)에 그 이름이 영원히 남음</t>
+          <t>50번의 결투에서 살아남아 목검(자유)을 받음</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>관중이 이름을 연호한 '모래판의 사자'로 기억됨</t>
         </is>
       </c>
     </row>
@@ -1557,27 +1743,32 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>바이킹 항해사</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>900년경</t>
+          <t>로마 군단의 군마</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>북대서양 항해 중 폭풍으로 실종</t>
+          <t>서기 100년경</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>해와 태양돌로 방향을 읽어 신대륙 해안에 닿음</t>
+          <t>원정 행군 중 늙어 쓰러짐</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>'서쪽 바다를 연 자'로 사가(saga)에 남음</t>
+          <t>장군을 태우고 갈리아 전역을 누빔</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>'멈추지 않는 발굽'으로 병사들에게 사랑받음</t>
         </is>
       </c>
     </row>
@@ -1587,27 +1778,32 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>몽골 기마 궁수</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>1220년경</t>
+          <t>켈트 숲의 흰 수사슴</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>원정 중 낙마로 사망</t>
+          <t>서기 100년경</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>초원을 가로지르며 활을 쏴 이름을 떨침</t>
+          <t>사냥꾼의 화살을 대신 맞고 새끼를 지킴</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>'바람보다 빠른 활'로 초원의 노래에 남음</t>
+          <t>달빛 아래 나타나 길 잃은 이를 숲 밖으로 인도</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>'숲의 정령'으로 켈트 전설에 남음</t>
         </is>
       </c>
     </row>
@@ -1617,27 +1813,32 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>고려 청자 도공</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>1200년경</t>
+          <t>고대 로마의 검투사 학교 의사</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>가마 불을 살피다 병으로 사망</t>
+          <t>서기 160년경</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>비색 상감청자의 신비로운 빛을 완성</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>'하늘빛을 구운 손'으로 후대 도공이 흠모함</t>
+          <t>부상당한 검투사를 치료하며 해부학을 익힘</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>'상처를 읽은 손'으로 의학사에 남음</t>
         </is>
       </c>
     </row>
@@ -1647,27 +1848,32 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>중세 연금술사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>1350년경</t>
+          <t>고대 로마의 모자이크 바닥 장인</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>수은 실험 중독으로 사망</t>
+          <t>서기 200년경</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>물질의 변환을 연구하며 화학의 씨앗을 뿌림</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>'금을 좇다 지혜를 남긴 자'로 기록됨</t>
+          <t>저택 바닥에 물고기와 신화를 조각조각 새김</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>'발밑에 그림을 깐 손'으로 유적에 남음</t>
         </is>
       </c>
     </row>
@@ -1677,27 +1883,32 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>흑사병 시대의 의사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>1348년경</t>
+          <t>마야 천문 사제</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>환자를 돌보다 흑사병에 감염되어 사망</t>
+          <t>서기 300년경</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>새 부리 가면을 쓰고 역병 환자를 끝까지 돌봄</t>
+          <t>제례 중 지진으로 신전과 함께 매몰</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>'죽음 곁을 지킨 손'으로 도시가 애도함</t>
+          <t>금성의 주기를 계산해 정교한 달력을 만듦</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>'하늘의 시간을 읽은 자'로 석비에 새겨짐</t>
         </is>
       </c>
     </row>
@@ -1707,27 +1918,32 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>대성당 석상 조각가</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>1250년경</t>
+          <t>사산조 페르시아 은세공사</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>높은 첨탑에서 작업 중 추락</t>
+          <t>서기 400년경</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>성당 처마에 수호 괴수상(가고일)을 새김</t>
+          <t>궁정 다툼에 휘말려 사망</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>'돌에 표정을 준 손'으로 성당과 함께 남음</t>
+          <t>왕의 사냥 장면을 새긴 은접시를 만듦</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>'은에 왕을 새긴 손'으로 유물에 남음</t>
         </is>
       </c>
     </row>
@@ -1737,27 +1953,32 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>실크로드 대상의 낙타</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>1300년경</t>
+          <t>고구려 고분 벽화 화공</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>사막 횡단 중 탈진으로 죽음</t>
+          <t>서기 500년경</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>무거운 짐을 지고 사막을 수십 번 건넘</t>
+          <t>무덤 작업 중 병으로 사망</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>'사막의 배'로 대상들에게 오래 이야기됨</t>
+          <t>무덤 벽에 사신도와 하늘 세계를 그림</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>'무덤에 하늘을 그린 손'으로 벽화에 남음</t>
         </is>
       </c>
     </row>
@@ -1767,27 +1988,32 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>일본 전국시대 사무라이</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>1550년경</t>
+          <t>고대 마야의 고무공 선수</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>주군을 지키다 전투에서 전사</t>
+          <t>서기 600년경</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>명예를 걸고 수많은 싸움을 치름</t>
+          <t>의례 경기 후 희생 제물이 됨</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>'충의 칼'로 가문의 족보에 남음</t>
+          <t>신성한 공놀이에서 뛰어난 실력을 보임</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>'신들의 경기자'로 벽 부조에 남음</t>
         </is>
       </c>
     </row>
@@ -1797,27 +2023,32 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>아즈텍 독수리 전사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>1450년경</t>
+          <t>당나라 장안의 기녀 예인</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>의식용 전투에서 포로가 되어 희생됨</t>
+          <t>750년경</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>태양신에게 바쳐진 용맹한 전사로 이름을 떨침</t>
+          <t>전란 속에 피란 중 병사</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>'태양의 독수리'로 벽화에 그려짐</t>
+          <t>비파와 시로 장안의 밤을 밝힘</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>'노래로 도성을 물들인 이'로 시에 남음</t>
         </is>
       </c>
     </row>
@@ -1827,27 +2058,32 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>잉카의 매듭 기록관(키푸카마욕)</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>1450년경</t>
+          <t>황금을 지키는 그리핀</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>800년경</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>매듭 끈으로 제국의 인구와 곡물을 기록</t>
+          <t>보물을 노린 도굴꾼과 싸우다 상처로 스러짐</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>'끈에 나라를 담은 자'로 구전에 남음</t>
+          <t>사자의 몸과 독수리의 날개로 산의 금맥을 지킴</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>'하늘과 땅의 파수꾼'으로 문장(紋章)에 새겨짐</t>
         </is>
       </c>
     </row>
@@ -1857,27 +2093,32 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>서아프리카의 그리오(음유 사관)</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>1300년경</t>
+          <t>수도원의 고양이 판구르 반</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>노환으로 마을에서 사망</t>
+          <t>850년경</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>왕들의 계보와 역사를 노래로 외워 전함</t>
+          <t>난롯가에서 노환으로 잠들 듯 죽음</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>'살아있는 역사책'으로 마을이 기림</t>
+          <t>필사실의 쥐를 지켜 수도사의 벗이 됨</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>한 수도사의 시(詩)에 그 이름이 영원히 남음</t>
         </is>
       </c>
     </row>
@@ -1887,27 +2128,32 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>중세 기사의 군마 데스트리에</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>1350년경</t>
+          <t>천년 묵은 구미호</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>마상 창시합 중 부상으로 죽음</t>
+          <t>900년경</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>갑옷을 두르고 주인을 태워 수많은 전장을 누빔</t>
+          <t>인간이 되려던 마지막 시험에서 스러짐</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>'강철의 발굽'으로 문장(紋章)에 남음</t>
+          <t>달밤마다 아홉 꼬리로 사람을 홀리고 또 지켜봄</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>'달빛 여우'로 옛이야기마다 되살아남</t>
         </is>
       </c>
     </row>
@@ -1917,27 +2163,32 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>아라비아의 천문학자</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>1000년경</t>
+          <t>바이킹 항해사</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>900년경</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>별의 목록을 정리하고 아스트롤라베를 개량</t>
+          <t>북대서양 항해 중 폭풍으로 실종</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>'별에 이름을 붙인 자'로 후대 학자가 인용함</t>
+          <t>해와 태양돌로 방향을 읽어 신대륙 해안에 닿음</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>'서쪽 바다를 연 자'로 사가(saga)에 남음</t>
         </is>
       </c>
     </row>
@@ -1947,27 +2198,32 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>비잔틴 모자이크 장인</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>1050년경</t>
+          <t>아라비아의 천문학자</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>성당 돔에서 작업 중 사고로 사망</t>
+          <t>1000년경</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>황금 유리 조각으로 성인의 얼굴을 완성</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>'빛으로 얼굴을 지은 손'으로 성당이 기억함</t>
+          <t>별의 목록을 정리하고 아스트롤라베를 개량</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>'별에 이름을 붙인 자'로 후대 학자가 인용함</t>
         </is>
       </c>
     </row>
@@ -1977,27 +2233,32 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>남프랑스의 음유시인</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>1180년경</t>
+          <t>중세 아라비아 상인의 대상 안내인</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>여행 중 노상에서 병으로 사망</t>
+          <t>1000년경</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>궁정을 떠돌며 사랑과 무용담을 노래함</t>
+          <t>사막에서 길을 잃고 갈증으로 사망</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>'사랑을 노래한 방랑자'로 시집에 남음</t>
+          <t>별과 모래언덕으로 대상의 길을 안내</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>'사막을 읽은 눈'으로 대상들이 기림</t>
         </is>
       </c>
     </row>
@@ -2007,27 +2268,32 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>송나라 화약 기술자</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>중세 베네딕토 수도원의 약초사</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
           <t>1150년경</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>화약 실험 중 폭발로 사망</t>
-        </is>
-      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>불화살과 초기 화기를 개량</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>'불을 다스린 손'으로 병서에 기록됨</t>
+          <t>수도원 정원에서 약초를 길러 병자를 돌봄</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>'정원의 치료사'로 약초서에 남음</t>
         </is>
       </c>
     </row>
@@ -2037,27 +2303,32 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>귀족의 사냥매(송골매)</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>1400년경</t>
+          <t>남프랑스의 음유시인</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>사냥 중 폭풍에 휩쓸려 실종</t>
+          <t>1180년경</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>하늘을 갈라 사냥감을 잡아 주인의 자랑이 됨</t>
+          <t>여행 중 노상에서 병으로 사망</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>'하늘의 화살'로 매사냥 이야기에 남음</t>
+          <t>궁정을 떠돌며 사랑과 무용담을 노래함</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>'사랑을 노래한 방랑자'로 시집에 남음</t>
         </is>
       </c>
     </row>
@@ -2067,27 +2338,32 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>대항해시대 지도 제작자</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>1520년경</t>
+          <t>강을 지키던 이무기</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>항해 중 괴혈병으로 사망</t>
+          <t>1200년경</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>새로 발견된 해안선을 지도에 그려 넣음</t>
+          <t>여의주를 얻지 못해 승천에 실패하고 강바닥에 잠듦</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>'세계를 종이에 담은 손'으로 해도에 이름을 남김</t>
+          <t>천 년을 물속에서 기다리며 강을 지킴</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>'용이 되지 못한 뱀'으로 강가 전설에 남음</t>
         </is>
       </c>
     </row>
@@ -2097,27 +2373,32 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>르네상스 프레스코 화가</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>1510년경</t>
+          <t>하와이의 원양 카누 항해사</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>천장화 작업 중 비계에서 떨어져 사망</t>
+          <t>1200년경</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>성당 천장에 거대한 벽화를 그림</t>
+          <t>먼 바다 항해 중 폭풍으로 실종</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>'천장에 하늘을 그린 손'으로 미술사에 남음</t>
+          <t>별과 파도만으로 태평양의 섬들을 잇는 항해</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>'별을 따라간 사람'으로 구전에 남음</t>
         </is>
       </c>
     </row>
@@ -2127,27 +2408,32 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>구텐베르크 인쇄공</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>1455년경</t>
+          <t>몽골 기마 궁수</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>납 활자 중독으로 건강을 잃고 사망</t>
+          <t>1220년경</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>활자를 짜 성서를 대량으로 인쇄</t>
+          <t>원정 중 낙마로 사망</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>'지식을 퍼뜨린 손'으로 인쇄술 역사에 남음</t>
+          <t>초원을 가로지르며 활을 쏴 이름을 떨침</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>'바람보다 빠른 활'로 초원의 노래에 남음</t>
         </is>
       </c>
     </row>
@@ -2157,27 +2443,32 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>모리셔스의 도도새</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>1660년경</t>
+          <t>몽골 제국의 역참 파발마</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>선원들의 남획으로 멸종</t>
+          <t>1250년경</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>천적 없는 섬에서 평화롭게 살아감</t>
+          <t>혹한의 전령 임무 중 쓰러져 죽음</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>'사라진 순한 새'로 멸종의 상징이 됨</t>
+          <t>제국의 끝에서 끝까지 소식을 실어 나름</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>'초원의 우편'으로 역사에 남음</t>
         </is>
       </c>
     </row>
@@ -2187,27 +2478,32 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>카리브해의 해적</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>1700년경</t>
+          <t>대성당 석상 조각가</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>해군과의 교전에서 전사</t>
+          <t>1250년경</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>보물선을 쫓아 카리브해를 누빔</t>
+          <t>높은 첨탑에서 작업 중 추락</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>'검은 깃발의 사나이'로 뱃노래에 남음</t>
+          <t>성당 처마에 수호 괴수상(가고일)을 새김</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>'돌에 표정을 준 손'으로 성당과 함께 남음</t>
         </is>
       </c>
     </row>
@@ -2217,27 +2513,32 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>범선의 배고양이</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>1690년경</t>
+          <t>중세 아이슬란드의 이야기꾼(사가 낭송가)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>긴 항해 끝 폭풍우에 갑판에서 실종</t>
+          <t>1250년경</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>선창의 쥐를 잡아 식량과 밧줄을 지킴</t>
+          <t>긴 겨울밤 노환으로 사망</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>선원들의 행운의 부적 '항해 고양이'로 기억됨</t>
+          <t>영웅들의 사가를 외워 화롯가에서 들려줌</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>'겨울밤의 목소리'로 사가에 남음</t>
         </is>
       </c>
     </row>
@@ -2247,27 +2548,32 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>네덜란드 튤립 상인</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>1637년경</t>
+          <t>실크로드 대상의 낙타</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>튤립 버블 붕괴로 파산해 실의 속에 사망</t>
+          <t>1300년경</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>한 송이가 집 한 채 값이던 튤립을 거래</t>
+          <t>사막 횡단 중 탈진으로 죽음</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>'꽃에 홀린 상인'으로 경제사에 이름이 남음</t>
+          <t>무거운 짐을 지고 사막을 수십 번 건넘</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>'사막의 배'로 대상들에게 오래 이야기됨</t>
         </is>
       </c>
     </row>
@@ -2277,27 +2583,32 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>조선 왕실 천문관</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>1440년경</t>
+          <t>숲을 지키는 유니콘</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>1300년경</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>간의와 혼천의로 하늘을 관측해 역법을 바로잡음</t>
+          <t>순수함이 사라진 시대에 숲 깊이 자취를 감춤</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>'하늘을 헤아린 신하'로 실록에 기록됨</t>
+          <t>이마의 뿔로 독을 정화하고 맑은 샘을 지킴</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>'순결의 짐승'으로 태피스트리에 짜여 남음</t>
         </is>
       </c>
     </row>
@@ -2307,27 +2618,32 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>에도의 우키요에 판목 조각사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>1760년경</t>
+          <t>서아프리카의 그리오(음유 사관)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>눈이 멀어 은퇴 후 사망</t>
+          <t>1300년경</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>화가의 그림을 목판에 새겨 다색 판화를 찍음</t>
+          <t>노환으로 마을에서 사망</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>'선을 새긴 손'으로 판화 뒤에 이름이 전함</t>
+          <t>왕들의 계보와 역사를 노래로 외워 전함</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>'살아있는 역사책'으로 마을이 기림</t>
         </is>
       </c>
     </row>
@@ -2337,27 +2653,32 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>일본 다도의 다도가</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>1580년경</t>
+          <t>중세 파리의 대학 필경 학생</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>정변에 휘말려 할복</t>
+          <t>1300년경</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>차 한 잔에 우주를 담는 다도를 정립</t>
+          <t>역병으로 젊어서 사망</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>'고요를 대접한 사람'으로 다실에 남음</t>
+          <t>강의를 받아적어 지식을 책으로 남김</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>'배움을 옮긴 손'으로 대학사에 남음</t>
         </is>
       </c>
     </row>
@@ -2367,27 +2688,32 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>북극해의 포경선원</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>1750년경</t>
+          <t>중세 기사의 군마 데스트리에</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>고래 사냥 중 밧줄에 끌려가 익사</t>
+          <t>1350년경</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>혹독한 북극해에서 고래를 잡아 기름을 얻음</t>
+          <t>마상 창시합 중 부상으로 죽음</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>'얼음 바다의 사냥꾼'으로 항구가 기억함</t>
+          <t>갑옷을 두르고 주인을 태워 수많은 전장을 누빔</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>'강철의 발굽'으로 문장(紋章)에 남음</t>
         </is>
       </c>
     </row>
@@ -2397,27 +2723,32 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>스텔러바다소</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>1768년경</t>
+          <t>중세 연금술사</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>발견 27년 만에 남획으로 멸종</t>
+          <t>1350년경</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>북태평양 차가운 바다에서 온순하게 살아감</t>
+          <t>수은 실험 중독으로 사망</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>'너무 빨리 사라진 거인'으로 기록에만 남음</t>
+          <t>물질의 변환을 연구하며 화학의 씨앗을 뿌림</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>'금을 좇다 지혜를 남긴 자'로 기록됨</t>
         </is>
       </c>
     </row>
@@ -2427,27 +2758,32 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>갈릴레오 시대의 망원경 장인</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>1620년경</t>
+          <t>귀족의 사냥매(송골매)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>1400년경</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>더 선명한 렌즈를 갈아 하늘을 가깝게 만듦</t>
+          <t>사냥 중 폭풍에 휩쓸려 실종</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>'하늘을 당겨준 손'으로 천문학자들이 고마워함</t>
+          <t>하늘을 갈라 사냥감을 잡아 주인의 자랑이 됨</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>'하늘의 화살'로 매사냥 이야기에 남음</t>
         </is>
       </c>
     </row>
@@ -2457,27 +2793,32 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>궁정의 어릿광대</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>1600년경</t>
+          <t>정원의 천 살 벚나무</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>왕을 웃기다 실언으로 추방된 뒤 병사</t>
+          <t>1400년경</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>웃음 속에 뼈 있는 진실을 왕에게 전함</t>
+          <t>큰 태풍에 오랜 줄기가 부러져 스러짐</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>'웃기는 현자'로 궁정 일화에 남음</t>
+          <t>해마다 온 마을을 분홍 꽃으로 뒤덮어 위로함</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>'봄마다 피는 약속'으로 마을이 기억함</t>
         </is>
       </c>
     </row>
@@ -2487,27 +2828,32 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>바로크 시대 파이프오르간 제작자</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>1710년경</t>
+          <t>아즈텍 독수리 전사</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>노환으로 작업실에서 사망</t>
+          <t>1450년경</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>성당의 거대한 파이프오르간을 만듦</t>
+          <t>의식용 전투에서 포로가 되어 희생됨</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>'교회에 목소리를 준 손'으로 악기에 새겨짐</t>
+          <t>태양신에게 바쳐진 용맹한 전사로 이름을 떨침</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>'태양의 독수리'로 벽화에 그려짐</t>
         </is>
       </c>
     </row>
@@ -2517,27 +2863,32 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>아메리카 대평원의 들소</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>1800년경</t>
+          <t>베네치아 유리 장인</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>서부 개척기 대규모 사냥으로 수가 급감</t>
+          <t>1450년경</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>수백만 마리 무리로 대평원을 뒤덮음</t>
+          <t>용광로 곁에서 노환으로 사망</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>'사라진 대평원의 주인'으로 원주민이 기림</t>
+          <t>무라노 섬에서 투명하고 색색인 유리를 불어 만듦</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>'불로 유리를 빚은 손'으로 섬이 기림</t>
         </is>
       </c>
     </row>
@@ -2547,27 +2898,32 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>청나라 경덕진 도자기 장인</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>1720년경</t>
+          <t>고대 안데스 잉카의 계단밭 농부</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>가마 곁에서 노환으로 사망</t>
+          <t>1450년경</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>청화백자를 구워 유럽 왕실까지 수출</t>
+          <t>산사태로 밭과 함께 매몰</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>'푸른 그림의 명장'으로 도자기에 낙관이 남음</t>
+          <t>가파른 산에 계단밭을 일궈 감자를 길러냄</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>'산을 밭으로 바꾼 손'으로 유적에 남음</t>
         </is>
       </c>
     </row>
@@ -2577,27 +2933,32 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>바흐 시대의 궁정 음악가</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>1740년경</t>
+          <t>구텐베르크 인쇄공</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>1455년경</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>궁정을 위해 수백 곡의 협주곡을 작곡</t>
+          <t>납 활자 중독으로 건강을 잃고 사망</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>'멜로디를 흘려보낸 사람'으로 악보에 남음</t>
+          <t>활자를 짜 성서를 대량으로 인쇄</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>'지식을 퍼뜨린 손'으로 인쇄술 역사에 남음</t>
         </is>
       </c>
     </row>
@@ -2607,27 +2968,32 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>프랑스 혁명기의 신문 인쇄인</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>1789년경</t>
+          <t>고성(古城)의 천 년 된 올리브나무</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>혁명의 혼란 속에 체포되어 처형됨</t>
+          <t>1500년경</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>거리에 소식을 찍어 돌려 민중을 깨움</t>
+          <t>벼락을 맞아 불타 쓰러짐</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>'활자로 외친 사람'으로 혁명사에 남음</t>
+          <t>천 년간 그늘과 열매를 사람들에게 내어줌</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>'말없는 증인'으로 마을 역사와 함께 기억됨</t>
         </is>
       </c>
     </row>
@@ -2637,27 +3003,32 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>증기기관차 기관사</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>1840년경</t>
+          <t>북해의 인어</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>탈선 사고에서 승객을 구하고 순직</t>
+          <t>1500년경</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>석탄을 때 도시와 도시를 강철 궤도로 이음</t>
+          <t>부서진 배의 선원을 구하려다 그물에 걸려 죽음</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>'철마를 몬 사나이'로 역사(驛舍)에 남음</t>
+          <t>노래로 뱃사람을 위험한 암초에서 돌려세움</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>'파도의 노래'로 뱃사람의 전설에 남음</t>
         </is>
       </c>
     </row>
@@ -2667,27 +3038,32 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>등대지기</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>1870년경</t>
+          <t>대숲을 이룬 대나무</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>폭풍우 치는 밤 등불을 지키다 병사</t>
+          <t>1500년경</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>40년간 하룻밤도 등불을 꺼뜨리지 않음</t>
+          <t>백 년에 한 번 꽃을 피우고 모두 함께 스러짐</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>'바다의 별을 지킨 사람'으로 뱃사람이 기림</t>
+          <t>곧게 자라 선비의 절개와 바람의 노래가 됨</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>'속이 빈 곧은 마음'으로 그림과 시에 남음</t>
         </is>
       </c>
     </row>
@@ -2697,27 +3073,32 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>전신 기사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>1860년경</t>
+          <t>안데스의 리마(라마) 몰이꾼</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>과로로 쓰러져 사망</t>
+          <t>1500년경</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>모스 부호로 대륙을 가로질러 소식을 전함</t>
+          <t>산길에서 눈사태에 휩쓸려 사망</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>'점과 선으로 말한 사람'으로 통신사에 남음</t>
+          <t>라마 떼에 짐을 지워 고산 마을을 이음</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>'구름 위의 길잡이'로 산마을이 기억함</t>
         </is>
       </c>
     </row>
@@ -2727,27 +3108,32 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>여행비둘기(패신저 피전)</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>1914년</t>
+          <t>대항해시대 지도 제작자</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>무분별한 사냥으로 마지막 개체 '마사'가 죽으며 멸종</t>
+          <t>1520년경</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>한때 하늘을 뒤덮을 만큼 거대한 무리를 이룸</t>
+          <t>항해 중 괴혈병으로 사망</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>'하늘을 가렸던 새'로 멸종의 경종이 됨</t>
+          <t>새로 발견된 해안선을 지도에 그려 넣음</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>'세계를 종이에 담은 손'으로 해도에 이름을 남김</t>
         </is>
       </c>
     </row>
@@ -2757,27 +3143,32 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>태즈메이니아 호랑이(틸라신)</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>1936년</t>
+          <t>오스만 제국의 세밀화가</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>동물원에서 마지막 개체가 죽어 멸종</t>
+          <t>1550년경</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>주머니를 가진 독특한 육식동물로 살아감</t>
+          <t>실명 후 은퇴하여 사망</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>'사라진 줄무늬'로 보존의 상징이 됨</t>
+          <t>술탄의 책에 정교한 세밀화를 그림</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>'붓끝의 궁정'으로 필사본에 남음</t>
         </is>
       </c>
     </row>
@@ -2787,27 +3178,32 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>제1차 세계대전의 전서구 셰르 아미</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>1918년</t>
+          <t>일본 다도의 다도가</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>전선을 넘다 총상을 입고 임무 후 사망</t>
+          <t>1580년경</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>포위된 부대의 구조 요청을 물고 날아 수백 명을 구함</t>
+          <t>정변에 휘말려 할복</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>'날개 달린 전령'으로 훈장을 받고 기려짐</t>
+          <t>차 한 잔에 우주를 담는 다도를 정립</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>'고요를 대접한 사람'으로 다실에 남음</t>
         </is>
       </c>
     </row>
@@ -2817,27 +3213,32 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>탄광 광부</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>1900년경</t>
+          <t>고향 강으로 돌아온 연어</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>갱도 붕괴 사고로 순직</t>
+          <t>1600년경</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>지하 깊은 곳에서 도시를 데울 석탄을 캠</t>
+          <t>산란을 마치고 강 상류에서 생을 마침</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>'땅속의 등불'로 광산 마을이 기억함</t>
+          <t>폭포를 거슬러 올라 태어난 강으로 되돌아옴</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>'돌아오는 은빛'으로 강마을이 해마다 기림</t>
         </is>
       </c>
     </row>
@@ -2847,27 +3248,32 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>무성영화 시대의 배우</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>1920년경</t>
+          <t>사막을 건넌 여왕개미</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>유성영화 시대에 잊혀 쓸쓸히 사망</t>
+          <t>1600년경</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>표정과 몸짓만으로 관객을 울리고 웃김</t>
+          <t>새 왕국을 세운 뒤 수명을 다해 죽음</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>'말 없는 스타'로 낡은 필름에 남음</t>
+          <t>홀로 날아올라 모래언덕 아래 거대한 왕국을 세움</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>'모래 아래 여왕'으로 대상들의 이야기에 남음</t>
         </is>
       </c>
     </row>
@@ -2877,27 +3283,32 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>1920년대 재즈 피아니스트</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>1929년경</t>
+          <t>조선의 명의 한의원</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>폐병으로 젊은 나이에 사망</t>
+          <t>1600년경</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>밤의 클럽에서 즉흥 연주로 시대를 흔듦</t>
+          <t>역병 환자를 돌보다 감염되어 사망</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>'건반 위의 자유'로 오래된 음반에 남음</t>
+          <t>의서를 집대성해 백성의 병을 다스림</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>'백성을 살린 손'으로 의서에 이름이 남음</t>
         </is>
       </c>
     </row>
@@ -2907,27 +3318,32 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>우주로 간 개 라이카</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>1957년</t>
+          <t>갈릴레오 시대의 망원경 장인</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>스푸트니크 2호 안에서 궤도 비행 중 사망</t>
+          <t>1620년경</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>지구 생명체 최초로 우주 궤도를 돎</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>'별이 된 개'로 우주 개척사에 영원히 남음</t>
+          <t>더 선명한 렌즈를 갈아 하늘을 가깝게 만듦</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>'하늘을 당겨준 손'으로 천문학자들이 고마워함</t>
         </is>
       </c>
     </row>
@@ -2937,27 +3353,32 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>눈보라를 뚫은 썰매개 발토</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>1925년</t>
+          <t>네덜란드 튤립 상인</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>임무 후 노환으로 죽음</t>
+          <t>1637년경</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>혈청을 싣고 눈보라 속 노메까지 달려 아이들을 구함</t>
+          <t>튤립 버블 붕괴로 파산해 실의 속에 사망</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>'생명을 나른 개'로 동상이 세워짐</t>
+          <t>한 송이가 집 한 채 값이던 튤립을 거래</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>'꽃에 홀린 상인'으로 경제사에 이름이 남음</t>
         </is>
       </c>
     </row>
@@ -2967,27 +3388,32 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>초기 여성 비행사</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>1930년경</t>
+          <t>모리셔스의 도도새</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>장거리 비행 중 바다 위에서 실종</t>
+          <t>1660년경</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>여성 최초로 대양 횡단 비행에 도전</t>
+          <t>선원들의 남획으로 멸종</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>'하늘을 연 여인'으로 항공사에 남음</t>
+          <t>천적 없는 섬에서 평화롭게 살아감</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>'사라진 순한 새'로 멸종의 상징이 됨</t>
         </is>
       </c>
     </row>
@@ -2997,27 +3423,32 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>스위치보드 전화 교환원</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>1940년경</t>
+          <t>범선의 배고양이</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>1690년경</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>수많은 통화를 손으로 이어 사람들을 연결</t>
+          <t>긴 항해 끝 폭풍우에 갑판에서 실종</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>'목소리를 이어준 손'으로 통신 초기사에 남음</t>
+          <t>선창의 쥐를 잡아 식량과 밧줄을 지킴</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>선원들의 행운의 부적 '항해 고양이'로 기억됨</t>
         </is>
       </c>
     </row>
@@ -3027,27 +3458,32 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>서커스의 코끼리</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>1910년경</t>
+          <t>처마 밑의 제비</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>혹사와 사고로 죽음</t>
+          <t>1700년경</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>천막 아래에서 관객에게 경이로움을 선사</t>
+          <t>먼 남쪽으로 가는 긴 여정 중 지쳐 떨어짐</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>'천막의 거인'으로 옛 포스터에 남음</t>
+          <t>해마다 같은 집 처마로 돌아와 복을 물어옴</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>'봄을 나르는 새'로 집집마다 반겨짐</t>
         </is>
       </c>
     </row>
@@ -3057,27 +3493,32 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>전설의 경주마</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>1945년경</t>
+          <t>이누이트 이글루 사냥꾼</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>은퇴 후 목장에서 노환으로 죽음</t>
+          <t>1700년경</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>불리한 출발에서도 역전 우승을 거듭함</t>
+          <t>얼음이 깨져 바다에 빠져 사망</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>'결승선의 심장'으로 경마사에 남음</t>
+          <t>작살로 물범을 잡아 혹한의 가족을 먹임</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>'얼음 위의 사냥꾼'으로 부족이 기림</t>
         </is>
       </c>
     </row>
@@ -3087,27 +3528,32 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>영화관 영사기사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>1950년경</t>
+          <t>조선 통신사의 역관</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>필름 화재 사고로 순직</t>
+          <t>1700년경</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>어두운 영사실에서 은막에 이야기를 비춤</t>
+          <t>사행길 바다에서 풍랑으로 사망</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>'빛으로 꿈을 쏜 사람'으로 극장이 기억함</t>
+          <t>일본과의 외교에서 말과 글을 이어줌</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>'두 나라를 이은 혀'로 사행록에 남음</t>
         </is>
       </c>
     </row>
@@ -3117,27 +3563,32 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>초기 라디오 방송인</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>1935년경</t>
+          <t>바로크 시대 파이프오르간 제작자</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>생방송 중 심장마비로 사망</t>
+          <t>1710년경</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>전파를 타고 온 나라에 목소리를 전함</t>
+          <t>노환으로 작업실에서 사망</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>'상자 속의 친구'로 청취자가 그리워함</t>
+          <t>성당의 거대한 파이프오르간을 만듦</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>'교회에 목소리를 준 손'으로 악기에 새겨짐</t>
         </is>
       </c>
     </row>
@@ -3147,27 +3598,32 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>2차 대전의 군마</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>1943년경</t>
+          <t>바흐 시대의 궁정 음악가</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>전장에서 포격으로 죽음</t>
+          <t>1740년경</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>포와 보급을 끌며 진창의 전선을 버팀</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>'말 없는 전우'로 참전 용사가 기림</t>
+          <t>궁정을 위해 수백 곡의 협주곡을 작곡</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>'멜로디를 흘려보낸 사람'으로 악보에 남음</t>
         </is>
       </c>
     </row>
@@ -3177,27 +3633,32 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>방직 공장의 여공</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>1920년경</t>
+          <t>조선의 궁중 화원</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>장시간 노동 끝에 병으로 사망</t>
+          <t>1750년경</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>밤낮으로 실을 자아 도시를 옷 입힘</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>'실을 짠 손'으로 노동사에 이름 없이 남음</t>
+          <t>임금의 행차와 풍속을 세밀히 그림</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>'붓으로 시대를 기록한 손'으로 화첩에 남음</t>
         </is>
       </c>
     </row>
@@ -3207,27 +3668,32 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>등대의 구조견</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>1900년경</t>
+          <t>프랑스 향수 조향사</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>난파선 구조 중 파도에 휩쓸려 죽음</t>
+          <t>1750년경</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>물에 빠진 선원들을 물어 뭍으로 끌어냄</t>
+          <t>향료 실험 중 병을 얻어 사망</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>'파도를 이긴 개'로 항구 마을이 기림</t>
+          <t>장미와 재스민을 섞어 왕비의 향수를 만듦</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>'향기를 지은 코'로 향수병에 이름이 남음</t>
         </is>
       </c>
     </row>
@@ -3237,27 +3703,32 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>초기 자동차 정비공</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>1915년경</t>
+          <t>에도의 우키요에 판목 조각사</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>엔진 사고로 부상 끝에 사망</t>
+          <t>1760년경</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>말없는 마차(자동차)를 고쳐 길 위에 올림</t>
+          <t>눈이 멀어 은퇴 후 사망</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>'쇠말을 살린 손'으로 정비소가 기억함</t>
+          <t>화가의 그림을 목판에 새겨 다색 판화를 찍음</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>'선을 새긴 손'으로 판화 뒤에 이름이 전함</t>
         </is>
       </c>
     </row>
@@ -3267,27 +3738,32 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>콰가(사라진 얼룩말)</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>1883년</t>
+          <t>스텔러바다소</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>남획으로 마지막 개체가 동물원에서 죽어 멸종</t>
+          <t>1768년경</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>반쯤 줄무늬를 가진 독특한 얼룩말로 초원을 누빔</t>
+          <t>발견 27년 만에 남획으로 멸종</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>'절반의 줄무늬'로 박제와 사진에만 남음</t>
+          <t>북태평양 차가운 바다에서 온순하게 살아감</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>'너무 빨리 사라진 거인'으로 기록에만 남음</t>
         </is>
       </c>
     </row>
@@ -3297,27 +3773,32 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>큰바다쇠오리(그레이트 오크)</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>1844년</t>
+          <t>아메리카 대평원의 들소</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>마지막 한 쌍이 수집가에게 잡혀 멸종</t>
+          <t>1800년경</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>북대서양 바위섬에서 헤엄치며 살아감</t>
+          <t>서부 개척기 대규모 사냥으로 수가 급감</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>'북쪽의 펭귄'으로 불리다 사라진 새로 남음</t>
+          <t>수백만 마리 무리로 대평원을 뒤덮음</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>'사라진 대평원의 주인'으로 원주민이 기림</t>
         </is>
       </c>
     </row>
@@ -3327,27 +3808,32 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>빅토리아 시대 굴뚝 청소 소년</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>1850년경</t>
+          <t>초기 등반 안내견</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>좁은 굴뚝에 갇혀 사고로 사망</t>
+          <t>1800년경</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>도시의 굴뚝을 청소해 화재를 막음</t>
+          <t>눈 속에 파묻힌 조난자를 구하다 죽음</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>'검댕 묻은 아이'로 시대의 아픔으로 기억됨</t>
+          <t>알프스 고개에서 조난자를 찾아 구조</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>'눈 속의 구원자'로 수도원이 기림</t>
         </is>
       </c>
     </row>
@@ -3357,27 +3843,32 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>초기 사진관 사진사</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>1880년경</t>
+          <t>남태평양의 늙은 바다거북</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>약품 중독으로 건강을 잃고 사망</t>
+          <t>1800년경</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>은판에 사람들의 얼굴을 영원히 담음</t>
+          <t>수백 년을 산 뒤 조용히 깊은 바다로 사라짐</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>'순간을 붙잡은 사람'으로 빛바랜 사진에 남음</t>
+          <t>대양을 가로질러 같은 모래해변으로 돌아와 알을 낳음</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>'바다의 어른'으로 섬사람들이 신성히 여김</t>
         </is>
       </c>
     </row>
@@ -3387,27 +3878,32 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>남극 탐험대의 썰매개</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>1912년경</t>
+          <t>조선의 줄타기 광대</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>탐험 도중 굶주림과 추위로 죽음</t>
+          <t>1800년경</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>탐험가를 태운 썰매를 끌고 극지를 횡단</t>
+          <t>장터 공연 중 줄에서 떨어져 사망</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>'얼음 대륙의 발'로 탐험 일지에 남음</t>
+          <t>허공의 줄 위에서 재담과 재주로 사람들을 홀림</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>'하늘을 걸은 광대'로 민속에 남음</t>
         </is>
       </c>
     </row>
@@ -3417,27 +3913,32 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>초기 영화 변사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>1925년경</t>
+          <t>초기 열기구 조종사</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>무성영화의 몰락과 함께 무대를 잃고 사망</t>
+          <t>1800년경</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>무성영화에 목소리로 극적인 해설을 입힘</t>
+          <t>기구가 찢어져 추락사</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>'스크린의 목소리'로 옛 극장가에 남음</t>
+          <t>인류 초기의 하늘을 열기구로 떠올랐음</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>'구름에 오른 사람'으로 비행사에 남음</t>
         </is>
       </c>
     </row>
@@ -3447,27 +3948,32 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>등대 근처의 우체부</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>1890년경</t>
+          <t>증기기관차 기관사</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>폭설 속 우편을 배달하다 조난</t>
+          <t>1840년경</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>산골과 섬마을에 편지를 빠짐없이 전함</t>
+          <t>탈선 사고에서 승객을 구하고 순직</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>'소식을 나른 발'로 마을이 오래 기림</t>
+          <t>석탄을 때 도시와 도시를 강철 궤도로 이음</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>'철마를 몬 사나이'로 역사(驛舍)에 남음</t>
         </is>
       </c>
     </row>
@@ -3477,27 +3983,32 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>직조기의 견습 방직공</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>1930년경</t>
+          <t>큰바다쇠오리(그레이트 오크)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>공장 화재로 사망</t>
+          <t>1844년</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>복잡한 무늬를 짜는 자카드 직기를 다룸</t>
+          <t>마지막 한 쌍이 수집가에게 잡혀 멸종</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>'무늬를 엮은 손'으로 직물에 남음</t>
+          <t>북대서양 바위섬에서 헤엄치며 살아감</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>'북쪽의 펭귄'으로 불리다 사라진 새로 남음</t>
         </is>
       </c>
     </row>
@@ -3507,27 +4018,32 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>초기 비행선 정비사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>1937년경</t>
+          <t>골드러시의 사금 채취꾼</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>비행선 폭발 사고로 순직</t>
+          <t>1849년경</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>하늘을 나는 거대한 비행선을 정비</t>
+          <t>강에서 사금을 캐다 급류에 휩쓸려 익사</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>'하늘의 배를 돌본 사람'으로 항공사에 남음</t>
+          <t>일확천금을 좇아 서부의 강을 뒤짐</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>'황금을 꿈꾼 사람'으로 개척사에 남음</t>
         </is>
       </c>
     </row>
@@ -3537,27 +4053,32 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>고대 인도 아유르베다 의사</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>기원전 200년경</t>
+          <t>대양의 향유고래</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>1850년경</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>약초와 명상으로 몸과 마음을 함께 치료</t>
+          <t>포경선의 작살에 맞아 죽음</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>'생명의 지혜를 전한 자'로 경전에 남음</t>
+          <t>깊은 바다를 잠수하며 대양을 누빈 거대한 고래</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>'심해의 노래'로 뱃사람 전설에 남음</t>
         </is>
       </c>
     </row>
@@ -3567,27 +4088,32 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>고대 중국 갑골 점술가</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>기원전 1200년경</t>
+          <t>정원을 날던 호랑나비</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>왕의 흉조 예언 후 문책받아 사망</t>
+          <t>1850년경</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>거북 등딱지에 새긴 갑골문으로 길흉을 점침</t>
+          <t>여름 끝자락 첫서리에 짧은 생을 마침</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>'뼈에 물음을 새긴 자'로 최초의 한자에 남음</t>
+          <t>이 꽃 저 꽃을 옮기며 정원에 열매를 맺게 함</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>'한 철의 춤'으로 화첩에 그려짐</t>
         </is>
       </c>
     </row>
@@ -3597,27 +4123,32 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>폼페이의 빵집 주인</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>서기 79년</t>
+          <t>빅토리아 시대 굴뚝 청소 소년</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>베수비오 화산 폭발로 화산재에 묻힘</t>
+          <t>1850년경</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>매일 아침 도시에 갓 구운 빵을 냄</t>
+          <t>좁은 굴뚝에 갇혀 사고로 사망</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>화산재 속 화덕과 함께 '멈춘 아침'으로 발굴됨</t>
+          <t>도시의 굴뚝을 청소해 화재를 막음</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>'검댕 묻은 아이'로 시대의 아픔으로 기억됨</t>
         </is>
       </c>
     </row>
@@ -3627,27 +4158,32 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>고대 그리스 도예가</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>기원전 500년경</t>
+          <t>조선의 보부상</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>1850년경</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>검은 형상 도기에 신화의 장면을 그림</t>
+          <t>장터를 오가다 산길에서 도적을 만나 사망</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>'항아리에 신화를 담은 손'으로 박물관에 남음</t>
+          <t>등짐을 지고 전국 장터에 물건과 소식을 나름</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>'길 위의 상인'으로 민중사에 남음</t>
         </is>
       </c>
     </row>
@@ -3657,27 +4193,32 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>사산조 페르시아 은세공사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>서기 400년경</t>
+          <t>초기 해저 케이블 부설선원</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>궁정 다툼에 휘말려 사망</t>
+          <t>1866년경</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>왕의 사냥 장면을 새긴 은접시를 만듦</t>
+          <t>대서양 한가운데 폭풍으로 실종</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>'은에 왕을 새긴 손'으로 유물에 남음</t>
+          <t>대륙을 잇는 전신 케이블을 바다 밑에 깖</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>'바다 밑에 길을 놓은 사람'으로 통신사에 남음</t>
         </is>
       </c>
     </row>
@@ -3687,27 +4228,32 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>고구려 고분 벽화 화공</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>서기 500년경</t>
+          <t>등대지기</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>무덤 작업 중 병으로 사망</t>
+          <t>1870년경</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>무덤 벽에 사신도와 하늘 세계를 그림</t>
+          <t>폭풍우 치는 밤 등불을 지키다 병사</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>'무덤에 하늘을 그린 손'으로 벽화에 남음</t>
+          <t>40년간 하룻밤도 등불을 꺼뜨리지 않음</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>'바다의 별을 지킨 사람'으로 뱃사람이 기림</t>
         </is>
       </c>
     </row>
@@ -3717,27 +4263,32 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>신라 석굴암 석공</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>751년경</t>
+          <t>서부의 역마차 마부</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>돌을 다루다 노환으로 사망</t>
+          <t>1870년경</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>화강암을 깎아 자비로운 불상을 완성</t>
+          <t>협곡에서 마차가 전복되어 사망</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>'돌에 미소를 새긴 손'으로 석굴에 전함</t>
+          <t>험로를 달려 우편과 승객을 실어 나름</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>'먼지 속의 길잡이'로 서부 전설에 남음</t>
         </is>
       </c>
     </row>
@@ -3747,27 +4298,32 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>당나라 장안의 기녀 예인</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>750년경</t>
+          <t>빅토리아 시대 식물 채집가</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>전란 속에 피란 중 병사</t>
+          <t>1870년경</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>비파와 시로 장안의 밤을 밝힘</t>
+          <t>정글 탐사 중 열병으로 사망</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>'노래로 도성을 물들인 이'로 시에 남음</t>
+          <t>세계를 돌며 희귀한 난초를 수집</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>'꽃을 좇은 모험가'로 식물도감에 남음</t>
         </is>
       </c>
     </row>
@@ -3777,27 +4333,32 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>중세 이슬람 도서관 번역가</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>830년경</t>
+          <t>초기 항구의 도선사</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>1880년경</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>그리스 철학서를 아랍어로 옮겨 지식을 보존</t>
+          <t>짙은 안개 속 좌초 사고로 사망</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>'지혜의 집을 채운 손'으로 학문사에 남음</t>
+          <t>큰 배를 좁은 항구로 안전히 이끎</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>'물길을 아는 사람'으로 항구가 기림</t>
         </is>
       </c>
     </row>
@@ -3807,27 +4368,32 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>베네치아 유리 장인</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>1450년경</t>
+          <t>초기 등록소의 지도 측량사</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>용광로 곁에서 노환으로 사망</t>
+          <t>1880년경</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>무라노 섬에서 투명하고 색색인 유리를 불어 만듦</t>
+          <t>오지 측량 중 사고로 사망</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>'불로 유리를 빚은 손'으로 섬이 기림</t>
+          <t>산과 들을 걸어 정확한 지도를 그림</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>'땅을 잰 발'로 지도에 남음</t>
         </is>
       </c>
     </row>
@@ -3837,27 +4403,32 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>잔다르크 시대의 종군 소녀</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>1429년경</t>
+          <t>콰가(사라진 얼룩말)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>전투 후 포로가 되어 처형됨</t>
+          <t>1883년</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>깃발을 들고 군대의 사기를 북돋움</t>
+          <t>남획으로 마지막 개체가 동물원에서 죽어 멸종</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>'불꽃 같은 소녀'로 전설에 남음</t>
+          <t>반쯤 줄무늬를 가진 독특한 얼룩말로 초원을 누빔</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>'절반의 줄무늬'로 박제와 사진에만 남음</t>
         </is>
       </c>
     </row>
@@ -3867,27 +4438,32 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>오스만 제국의 세밀화가</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>1550년경</t>
+          <t>초기 소방마차의 소방마</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>실명 후 은퇴하여 사망</t>
+          <t>1890년경</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>술탄의 책에 정교한 세밀화를 그림</t>
+          <t>화재 진압 출동 중 사고로 죽음</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>'붓끝의 궁정'으로 필사본에 남음</t>
+          <t>무거운 소방 펌프를 끌고 불길로 달려감</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>'불로 달린 말'로 소방서가 기림</t>
         </is>
       </c>
     </row>
@@ -3897,27 +4473,32 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>무굴 제국의 궁정 건축가</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>1640년경</t>
+          <t>초기 자연사 박물관 표본사</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>대공사 후 과로로 사망</t>
+          <t>1890년경</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>흰 대리석 영묘(타지마할 계열)를 설계</t>
+          <t>약품 중독으로 사망</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>'대리석에 사랑을 지은 손'으로 건축에 남음</t>
+          <t>멸종해 가는 동물을 정교한 표본으로 남김</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>'사라짐을 기록한 손'으로 박물관에 남음</t>
         </is>
       </c>
     </row>
@@ -3927,27 +4508,32 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>조선의 궁중 화원</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>1750년경</t>
+          <t>등대의 구조견</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>1900년경</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>임금의 행차와 풍속을 세밀히 그림</t>
+          <t>난파선 구조 중 파도에 휩쓸려 죽음</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>'붓으로 시대를 기록한 손'으로 화첩에 남음</t>
+          <t>물에 빠진 선원들을 물어 뭍으로 끌어냄</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>'파도를 이긴 개'로 항구 마을이 기림</t>
         </is>
       </c>
     </row>
@@ -3957,27 +4543,32 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>조선의 명의 한의원</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>1600년경</t>
+          <t>금붕어 연못의 비단잉어</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>역병 환자를 돌보다 감염되어 사망</t>
+          <t>1900년경</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>의서를 집대성해 백성의 병을 다스림</t>
+          <t>연못이 얼어 겨울에 죽음</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>'백성을 살린 손'으로 의서에 이름이 남음</t>
+          <t>정원 연못에서 화려한 비늘로 사람들을 즐겁게 함</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>'물속의 비단'으로 정원 그림에 남음</t>
         </is>
       </c>
     </row>
@@ -3987,27 +4578,32 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>발트해의 호박 채취인</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>1300년경</t>
+          <t>탄광 광부</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>겨울 바다에서 호박을 줍다 얼어 죽음</t>
+          <t>1900년경</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>파도가 실어온 호박을 모아 장신구로 만듦</t>
+          <t>갱도 붕괴 사고로 순직</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>'바다의 보석을 주운 이'로 마을이 기림</t>
+          <t>지하 깊은 곳에서 도시를 데울 석탄을 캠</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>'땅속의 등불'로 광산 마을이 기억함</t>
         </is>
       </c>
     </row>
@@ -4017,27 +4613,32 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>안데스의 리마(라마) 몰이꾼</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>1500년경</t>
+          <t>초기 사진 신문 기자</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>산길에서 눈사태에 휩쓸려 사망</t>
+          <t>1900년경</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>라마 떼에 짐을 지워 고산 마을을 이음</t>
+          <t>취재 중 사고로 사망</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>'구름 위의 길잡이'로 산마을이 기억함</t>
+          <t>카메라로 사건 현장을 세상에 알림</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>'셔터로 진실을 남긴 사람'으로 신문에 남음</t>
         </is>
       </c>
     </row>
@@ -4047,27 +4648,32 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>에도의 소방수(정화)</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>1700년경</t>
+          <t>초기 기상 관측원</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>대화재 진압 중 순직</t>
+          <t>1900년경</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>지붕을 부수며 큰 불의 확산을 막음</t>
+          <t>산정 관측소에서 폭풍에 고립되어 사망</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>'불과 싸운 사나이'로 우키요에에 남음</t>
+          <t>매일 하늘과 기압을 기록해 날씨를 예보</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>'하늘을 기록한 사람'으로 기상사에 남음</t>
         </is>
       </c>
     </row>
@@ -4077,27 +4683,32 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>프랑스 향수 조향사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>1750년경</t>
+          <t>아마존의 고무 채취공</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>향료 실험 중 병을 얻어 사망</t>
+          <t>1900년경</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>장미와 재스민을 섞어 왕비의 향수를 만듦</t>
+          <t>정글에서 열대병으로 사망</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>'향기를 지은 코'로 향수병에 이름이 남음</t>
+          <t>고무나무 수액을 받아 세계의 바퀴를 굴림</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>'정글의 땀'으로 고무 역사에 남음</t>
         </is>
       </c>
     </row>
@@ -4107,27 +4718,32 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>빈의 왈츠 작곡가</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>1860년경</t>
+          <t>메이지 시대 인력거꾼</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>1900년경</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>무도회장을 휘감는 경쾌한 왈츠를 작곡</t>
+          <t>과로로 길에서 쓰러져 사망</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>'도시를 춤추게 한 사람'으로 악보에 남음</t>
+          <t>손님을 태우고 도시의 골목을 달림</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>'두 다리의 마차'로 옛 사진에 남음</t>
         </is>
       </c>
     </row>
@@ -4137,27 +4753,32 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>골드러시의 사금 채취꾼</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>1849년경</t>
+          <t>서커스의 코끼리</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>강에서 사금을 캐다 급류에 휩쓸려 익사</t>
+          <t>1910년경</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>일확천금을 좇아 서부의 강을 뒤짐</t>
+          <t>혹사와 사고로 죽음</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>'황금을 꿈꾼 사람'으로 개척사에 남음</t>
+          <t>천막 아래에서 관객에게 경이로움을 선사</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>'천막의 거인'으로 옛 포스터에 남음</t>
         </is>
       </c>
     </row>
@@ -4167,27 +4788,32 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>남북전쟁의 종군 간호사</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>1863년경</t>
+          <t>남극 탐험대의 썰매개</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>부상병을 돌보다 전염병으로 사망</t>
+          <t>1912년경</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>야전 병원에서 수많은 병사를 간호</t>
+          <t>탐험 도중 굶주림과 추위로 죽음</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>'전장의 등불'로 병사들이 기림</t>
+          <t>탐험가를 태운 썰매를 끌고 극지를 횡단</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>'얼음 대륙의 발'로 탐험 일지에 남음</t>
         </is>
       </c>
     </row>
@@ -4197,27 +4823,32 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>서부의 역마차 마부</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>1870년경</t>
+          <t>여행비둘기(패신저 피전)</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>협곡에서 마차가 전복되어 사망</t>
+          <t>1914년</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>험로를 달려 우편과 승객을 실어 나름</t>
+          <t>무분별한 사냥으로 마지막 개체 '마사'가 죽으며 멸종</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>'먼지 속의 길잡이'로 서부 전설에 남음</t>
+          <t>한때 하늘을 뒤덮을 만큼 거대한 무리를 이룸</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>'하늘을 가렸던 새'로 멸종의 경종이 됨</t>
         </is>
       </c>
     </row>
@@ -4227,27 +4858,32 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>일본 홋카이도의 아이누 사냥꾼</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>1850년경</t>
+          <t>초기 자동차 정비공</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>겨울 산에서 곰 사냥 중 사망</t>
+          <t>1915년경</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>숲의 신에게 감사하며 자연과 공존</t>
+          <t>엔진 사고로 부상 끝에 사망</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>'숲의 아들'로 부족의 노래에 남음</t>
+          <t>말없는 마차(자동차)를 고쳐 길 위에 올림</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>'쇠말을 살린 손'으로 정비소가 기억함</t>
         </is>
       </c>
     </row>
@@ -4257,27 +4893,32 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>하와이의 원양 카누 항해사</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>1200년경</t>
+          <t>제1차 세계대전의 전서구 셰르 아미</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>먼 바다 항해 중 폭풍으로 실종</t>
+          <t>1918년</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>별과 파도만으로 태평양의 섬들을 잇는 항해</t>
+          <t>전선을 넘다 총상을 입고 임무 후 사망</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>'별을 따라간 사람'으로 구전에 남음</t>
+          <t>포위된 부대의 구조 요청을 물고 날아 수백 명을 구함</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>'날개 달린 전령'으로 훈장을 받고 기려짐</t>
         </is>
       </c>
     </row>
@@ -4287,27 +4928,32 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>초기 사진 신문 기자</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>1900년경</t>
+          <t>초기 재봉틀 공장의 재단사</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>취재 중 사고로 사망</t>
+          <t>1920년경</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>카메라로 사건 현장을 세상에 알림</t>
+          <t>과로로 병을 얻어 사망</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>'셔터로 진실을 남긴 사람'으로 신문에 남음</t>
+          <t>재봉틀로 기성복 시대의 문을 엶</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>'옷을 지은 손'으로 산업사에 남음</t>
         </is>
       </c>
     </row>
@@ -4317,27 +4963,32 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>초기 여성 타이피스트</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>1925년경</t>
+          <t>눈보라를 뚫은 썰매개 발토</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>1925년</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>타자기로 사무실의 서류를 빠르게 옮김</t>
+          <t>임무 후 노환으로 죽음</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>'또각또각 시대를 친 손'으로 사무 역사에 남음</t>
+          <t>혈청을 싣고 눈보라 속 노메까지 달려 아이들을 구함</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>'생명을 나른 개'로 동상이 세워짐</t>
         </is>
       </c>
     </row>
@@ -4347,27 +4998,32 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>초기 항공 우편 조종사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>1927년경</t>
+          <t>초기 영화 변사</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>야간 비행 중 악천후로 추락</t>
+          <t>1925년경</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>밤하늘을 가르며 편지를 대륙 너머로 실어 나름</t>
+          <t>무성영화의 몰락과 함께 무대를 잃고 사망</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>'하늘의 우체부'로 비행사들이 기림</t>
+          <t>무성영화에 목소리로 극적인 해설을 입힘</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>'스크린의 목소리'로 옛 극장가에 남음</t>
         </is>
       </c>
     </row>
@@ -4377,27 +5033,32 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>금붕어 연못의 비단잉어</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>1900년경</t>
+          <t>초기 항공 우편 조종사</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>연못이 얼어 겨울에 죽음</t>
+          <t>1927년경</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>정원 연못에서 화려한 비늘로 사람들을 즐겁게 함</t>
+          <t>야간 비행 중 악천후로 추락</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>'물속의 비단'으로 정원 그림에 남음</t>
+          <t>밤하늘을 가르며 편지를 대륙 너머로 실어 나름</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>'하늘의 우체부'로 비행사들이 기림</t>
         </is>
       </c>
     </row>
@@ -4407,27 +5068,32 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>양봉가의 꿀벌 여왕</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>1930년경</t>
+          <t>1920년대 재즈 피아니스트</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>겨울 벌통에서 수명을 다해 죽음</t>
+          <t>1929년경</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>수만 마리 일벌을 이끌며 꽃밭을 꿀로 바꿈</t>
+          <t>폐병으로 젊은 나이에 사망</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>'단맛을 지은 여왕'으로 벌통마다 이야기됨</t>
+          <t>밤의 클럽에서 즉흥 연주로 시대를 흔듦</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>'건반 위의 자유'로 오래된 음반에 남음</t>
         </is>
       </c>
     </row>
@@ -4437,27 +5103,32 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>고성(古城)의 천 년 된 올리브나무</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>1500년경</t>
+          <t>양봉가의 꿀벌 여왕</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>벼락을 맞아 불타 쓰러짐</t>
+          <t>1930년경</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>천 년간 그늘과 열매를 사람들에게 내어줌</t>
+          <t>겨울 벌통에서 수명을 다해 죽음</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>'말없는 증인'으로 마을 역사와 함께 기억됨</t>
+          <t>수만 마리 일벌을 이끌며 꽃밭을 꿀로 바꿈</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>'단맛을 지은 여왕'으로 벌통마다 이야기됨</t>
         </is>
       </c>
     </row>
@@ -4467,27 +5138,32 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>몽골 초원의 유목민 마두금 연주자</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>1600년경</t>
+          <t>직조기의 견습 방직공</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>혹독한 겨울 이동 중 병사</t>
+          <t>1930년경</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>말의 갈기로 만든 현으로 초원의 노래를 켬</t>
+          <t>공장 화재로 사망</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>'바람을 연주한 사람'으로 초원이 기림</t>
+          <t>복잡한 무늬를 짜는 자카드 직기를 다룸</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>'무늬를 엮은 손'으로 직물에 남음</t>
         </is>
       </c>
     </row>
@@ -4497,27 +5173,32 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>이누이트 이글루 사냥꾼</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>1700년경</t>
+          <t>초기 영화 스턴트맨</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>얼음이 깨져 바다에 빠져 사망</t>
+          <t>1930년경</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>작살로 물범을 잡아 혹한의 가족을 먹임</t>
+          <t>위험한 촬영 중 사고로 사망</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>'얼음 위의 사냥꾼'으로 부족이 기림</t>
+          <t>몸을 던져 스크린의 아찔한 장면을 완성</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>'대신 떨어진 사람'으로 영화 뒤에 남음</t>
         </is>
       </c>
     </row>
@@ -4527,27 +5208,32 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>고래잡이 배의 망꾼</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>1820년경</t>
+          <t>초기 만화 신문 삽화가</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>돛대 위에서 폭풍에 떨어져 사망</t>
+          <t>1930년경</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>가장 먼저 고래의 물기둥을 발견해 외침</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>'바다를 읽은 눈'으로 선원들이 기림</t>
+          <t>신문 한 칸에 세태를 풍자하는 만화를 그림</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>'한 칸의 웃음'으로 신문 스크랩에 남음</t>
         </is>
       </c>
     </row>
@@ -4557,27 +5243,32 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>초기 기상 관측원</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>1900년경</t>
+          <t>초기 우편 비행기의 정비사</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>산정 관측소에서 폭풍에 고립되어 사망</t>
+          <t>1930년경</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>매일 하늘과 기압을 기록해 날씨를 예보</t>
+          <t>격납고 사고로 사망</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>'하늘을 기록한 사람'으로 기상사에 남음</t>
+          <t>밤을 새워 우편기를 정비해 하늘길을 지킴</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>'하늘길의 손'으로 항공 우편사에 남음</t>
         </is>
       </c>
     </row>
@@ -4587,27 +5278,32 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>실크로드의 오아시스 대추야자 농부</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>800년경</t>
+          <t>초기 라디오 방송인</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>사막 마을의 가뭄으로 사망</t>
+          <t>1935년경</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>오아시스에 대추야자를 길러 대상을 먹임</t>
+          <t>생방송 중 심장마비로 사망</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>'사막의 단 열매'를 키운 이로 전해짐</t>
+          <t>전파를 타고 온 나라에 목소리를 전함</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>'상자 속의 친구'로 청취자가 그리워함</t>
         </is>
       </c>
     </row>
@@ -4617,27 +5313,32 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>고대 로마의 검투사 학교 의사</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>서기 160년경</t>
+          <t>초기 유성영화 음향 기사</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>노환으로 사망</t>
+          <t>1935년경</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>부상당한 검투사를 치료하며 해부학을 익힘</t>
+          <t>장비 사고로 감전되어 사망</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>'상처를 읽은 손'으로 의학사에 남음</t>
+          <t>화면에 처음으로 소리를 입히는 기술을 다룸</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>'스크린에 소리를 준 손'으로 영화사에 남음</t>
         </is>
       </c>
     </row>
@@ -4647,27 +5348,32 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>중세 유럽의 종치기</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>1200년경</t>
+          <t>태즈메이니아 호랑이(틸라신)</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>종탑에서 노환으로 사망</t>
+          <t>1936년</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>때에 맞춰 마을의 종을 울려 시간을 알림</t>
+          <t>동물원에서 마지막 개체가 죽어 멸종</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>'시간을 울린 사람'으로 종탑에 남음</t>
+          <t>주머니를 가진 독특한 육식동물로 살아감</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>'사라진 줄무늬'로 보존의 상징이 됨</t>
         </is>
       </c>
     </row>
@@ -4677,27 +5383,32 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>조선 통신사의 역관</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>1700년경</t>
+          <t>스위치보드 전화 교환원</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>사행길 바다에서 풍랑으로 사망</t>
+          <t>1940년경</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>일본과의 외교에서 말과 글을 이어줌</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>'두 나라를 이은 혀'로 사행록에 남음</t>
+          <t>수많은 통화를 손으로 이어 사람들을 연결</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>'목소리를 이어준 손'으로 통신 초기사에 남음</t>
         </is>
       </c>
     </row>
@@ -4707,27 +5418,32 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>초기 영화 스턴트맨</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>1930년경</t>
+          <t>초기 라디오 조립 기술자</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>위험한 촬영 중 사고로 사망</t>
+          <t>1940년경</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>몸을 던져 스크린의 아찔한 장면을 완성</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>'대신 떨어진 사람'으로 영화 뒤에 남음</t>
+          <t>가정마다 라디오를 조립해 세상 소식을 들여옴</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>'상자에 세상을 담은 손'으로 기억됨</t>
         </is>
       </c>
     </row>
@@ -4737,27 +5453,32 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>등대섬의 양치기</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>1850년경</t>
+          <t>2차 대전의 군마</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>절벽에서 양을 구하려다 추락</t>
+          <t>1943년경</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>외딴 섬에서 양 떼를 돌보며 홀로 살아감</t>
+          <t>전장에서 포격으로 죽음</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>'섬의 목자'로 뱃사람들이 기림</t>
+          <t>포와 보급을 끌며 진창의 전선을 버팀</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>'말 없는 전우'로 참전 용사가 기림</t>
         </is>
       </c>
     </row>
@@ -4767,27 +5488,32 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>초기 수족관의 흰돌고래</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>1960년경</t>
+          <t>전설의 경주마</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>수족관에서 병으로 죽음</t>
+          <t>1945년경</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>관객에게 처음으로 흰고래의 노래를 들려줌</t>
+          <t>은퇴 후 목장에서 노환으로 죽음</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>'바다의 노래꾼'으로 아이들 기억에 남음</t>
+          <t>불리한 출발에서도 역전 우승을 거듭함</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>'결승선의 심장'으로 경마사에 남음</t>
         </is>
       </c>
     </row>
@@ -4797,27 +5523,32 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>빅토리아 시대 식물 채집가</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>1870년경</t>
+          <t>초기 백신 연구 조수</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>정글 탐사 중 열병으로 사망</t>
+          <t>1950년경</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>세계를 돌며 희귀한 난초를 수집</t>
+          <t>실험실 감염으로 사망</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>'꽃을 좇은 모험가'로 식물도감에 남음</t>
+          <t>아이들을 살릴 백신 연구를 도움</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>'병을 몰아낸 손 중 하나'로 의학사에 남음</t>
         </is>
       </c>
     </row>
@@ -4827,27 +5558,32 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>초기 전화 발명 조수</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>1876년경</t>
+          <t>초기 등산 셰르파</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>실험 사고로 부상 끝에 사망</t>
+          <t>1953년경</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>멀리 목소리를 보내는 장치를 함께 만듦</t>
+          <t>고봉 원정 중 눈사태로 사망</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>'목소리에 날개를 단 손'으로 발명사에 남음</t>
+          <t>무거운 짐을 지고 세계의 지붕을 오름</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>'산이 사랑한 사람'으로 산악사에 남음</t>
         </is>
       </c>
     </row>
@@ -4857,27 +5593,32 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>아마존의 고무 채취공</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>1900년경</t>
+          <t>우주로 간 개 라이카</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>정글에서 열대병으로 사망</t>
+          <t>1957년</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>고무나무 수액을 받아 세계의 바퀴를 굴림</t>
+          <t>스푸트니크 2호 안에서 궤도 비행 중 사망</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>'정글의 땀'으로 고무 역사에 남음</t>
+          <t>지구 생명체 최초로 우주 궤도를 돎</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>'별이 된 개'로 우주 개척사에 영원히 남음</t>
         </is>
       </c>
     </row>
@@ -4887,27 +5628,32 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>초기 자동차 경주 드라이버</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>1930년경</t>
+          <t>초기 남극 기지 요리사</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>경주 중 충돌 사고로 사망</t>
+          <t>1958년경</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>먼지 자욱한 트랙에서 속도의 한계에 도전</t>
+          <t>기지 화재 사고로 사망</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>'질주의 심장'으로 모터스포츠사에 남음</t>
+          <t>혹한의 대원들에게 따뜻한 한 끼를 냄</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>'얼음 대륙의 부엌'으로 대원들이 기림</t>
         </is>
       </c>
     </row>
@@ -4917,27 +5663,32 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>이집트 파라오의 사냥개</t>
+          <t>생물</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>기원전 1400년경</t>
+          <t>초기 수족관의 흰돌고래</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>노환으로 죽어 주인 곁에 묻힘</t>
+          <t>1960년경</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>사냥터에서 파라오를 도와 짐승을 몰았음</t>
+          <t>수족관에서 병으로 죽음</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>'왕의 발치를 지킨 개'로 무덤 벽화에 남음</t>
+          <t>관객에게 처음으로 흰고래의 노래를 들려줌</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>'바다의 노래꾼'으로 아이들 기억에 남음</t>
         </is>
       </c>
     </row>
@@ -4947,27 +5698,32 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>초기 등산 셰르파</t>
+          <t>사람</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>1953년경</t>
+          <t>초기 동물원의 판다 사육사</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>고봉 원정 중 눈사태로 사망</t>
+          <t>1970년경</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>무거운 짐을 지고 세계의 지붕을 오름</t>
+          <t>노환으로 사망</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>'산이 사랑한 사람'으로 산악사에 남음</t>
+          <t>낯선 땅에 온 판다를 정성껏 돌봄</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>'대나무 곰의 친구'로 아이들이 기억함</t>
         </is>
       </c>
     </row>
